--- a/data/BRM.xlsx
+++ b/data/BRM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-27 PGDM 2nd Year\Ravinder sir\2025-27 TERM 5\Attendance sheet of term-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F574B0-012E-4958-8D1C-F4256717A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F701D4DC-A99F-4765-8310-C5CBFA7CA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{7F7ADE42-7E02-4ACE-BDAF-072FCF0085B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7F7ADE42-7E02-4ACE-BDAF-072FCF0085B8}"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="1" r:id="rId1"/>
@@ -40,15 +40,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="764">
   <si>
     <t>Roll No</t>
   </si>
@@ -2337,13 +2334,16 @@
   </si>
   <si>
     <t>pgdm25chaitanya_s@mdi.ac.in</t>
+  </si>
+  <si>
+    <t>Sritam Tripathy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2362,6 +2362,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2403,16 +2409,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2420,10 +2423,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3001,13 +3000,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D782EA-04BF-4256-B552-D0FEDBBC4F36}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>478</v>
       </c>
@@ -3018,758 +3017,758 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A64" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="3" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3795,13 +3794,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132D20A1-11BF-47DC-9E7A-59754E11F5DA}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="2"/>
-    <col min="3" max="3" width="18.85546875" style="2" customWidth="1"/>
+    <col min="1" max="2" width="9.1796875" style="2"/>
+    <col min="3" max="3" width="18.81640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>478</v>
       </c>
@@ -3812,758 +3811,758 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A64" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="3" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="3" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="3" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="59" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="62" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="3" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4585,14 +4584,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63A100B-9F76-4683-AB64-C9D629BF61B5}">
-  <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="2"/>
-    <col min="3" max="3" width="20.42578125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="9.1796875" style="2"/>
+    <col min="3" max="3" width="20.453125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>479</v>
       </c>
@@ -4603,771 +4602,783 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A65" si="0">A3+1</f>
+        <f t="shared" ref="A4:A66" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="3" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="3" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="3" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="3" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="3" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="59" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="3" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="62" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="65" spans="1:3" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="3" t="s">
         <v>341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -5376,17 +5387,18 @@
       <sortCondition ref="B1:B58"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B66:B1048576">
+  <conditionalFormatting sqref="B1 B67:B1048576">
     <cfRule type="duplicateValues" dxfId="19" priority="13"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B50:B51">
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B54 B46:B49 B2:B31 B52 B56:B58">
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B51">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5395,14 +5407,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9C8CCF-F8AD-4ED2-9483-C31DA582975B}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>479</v>
       </c>
@@ -5413,758 +5425,758 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A64" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="3" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="3" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="3" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="3" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="3" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="3" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="3" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="3" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="59" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="3" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="3" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="62" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="63" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="64" spans="1:3" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="3" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6174,14 +6186,14 @@
       <sortCondition ref="B1:B54"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
     <cfRule type="duplicateValues" dxfId="13" priority="5"/>
@@ -6203,15 +6215,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD20A25-06FB-4091-9401-2A12CBA0E826}">
   <dimension ref="A1:E254"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>478</v>
       </c>
@@ -6228,7 +6240,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -6241,11 +6253,11 @@
       <c r="D2" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -6258,11 +6270,11 @@
       <c r="D3" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -6275,11 +6287,11 @@
       <c r="D4" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -6292,11 +6304,11 @@
       <c r="D5" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -6309,11 +6321,11 @@
       <c r="D6" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -6326,11 +6338,11 @@
       <c r="D7" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -6343,11 +6355,11 @@
       <c r="D8" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -6360,11 +6372,11 @@
       <c r="D9" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -6377,11 +6389,11 @@
       <c r="D10" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -6394,11 +6406,11 @@
       <c r="D11" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -6411,11 +6423,11 @@
       <c r="D12" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -6428,11 +6440,11 @@
       <c r="D13" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -6445,11 +6457,11 @@
       <c r="D14" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -6462,11 +6474,11 @@
       <c r="D15" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -6479,11 +6491,11 @@
       <c r="D16" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -6496,11 +6508,11 @@
       <c r="D17" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -6513,11 +6525,11 @@
       <c r="D18" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -6530,11 +6542,11 @@
       <c r="D19" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -6547,11 +6559,11 @@
       <c r="D20" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -6564,11 +6576,11 @@
       <c r="D21" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -6581,11 +6593,11 @@
       <c r="D22" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -6598,11 +6610,11 @@
       <c r="D23" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -6615,11 +6627,11 @@
       <c r="D24" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -6632,11 +6644,11 @@
       <c r="D25" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -6649,11 +6661,11 @@
       <c r="D26" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -6666,11 +6678,11 @@
       <c r="D27" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -6683,11 +6695,11 @@
       <c r="D28" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -6700,11 +6712,11 @@
       <c r="D29" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -6717,11 +6729,11 @@
       <c r="D30" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -6734,11 +6746,11 @@
       <c r="D31" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -6751,11 +6763,11 @@
       <c r="D32" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -6768,11 +6780,11 @@
       <c r="D33" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -6785,11 +6797,11 @@
       <c r="D34" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E34" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -6802,11 +6814,11 @@
       <c r="D35" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -6819,11 +6831,11 @@
       <c r="D36" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -6836,11 +6848,11 @@
       <c r="D37" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -6853,11 +6865,11 @@
       <c r="D38" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -6870,11 +6882,11 @@
       <c r="D39" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -6887,11 +6899,11 @@
       <c r="D40" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -6904,11 +6916,11 @@
       <c r="D41" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -6921,11 +6933,11 @@
       <c r="D42" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -6938,11 +6950,11 @@
       <c r="D43" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -6955,11 +6967,11 @@
       <c r="D44" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -6972,11 +6984,11 @@
       <c r="D45" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -6989,11 +7001,11 @@
       <c r="D46" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -7006,11 +7018,11 @@
       <c r="D47" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -7023,11 +7035,11 @@
       <c r="D48" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -7040,11 +7052,11 @@
       <c r="D49" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -7057,11 +7069,11 @@
       <c r="D50" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -7074,11 +7086,11 @@
       <c r="D51" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -7091,11 +7103,11 @@
       <c r="D52" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -7108,11 +7120,11 @@
       <c r="D53" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -7125,11 +7137,11 @@
       <c r="D54" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -7142,11 +7154,11 @@
       <c r="D55" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -7159,11 +7171,11 @@
       <c r="D56" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E56" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -7176,11 +7188,11 @@
       <c r="D57" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E57" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -7193,11 +7205,11 @@
       <c r="D58" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E58" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -7210,11 +7222,11 @@
       <c r="D59" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E59" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -7227,11 +7239,11 @@
       <c r="D60" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E60" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -7244,11 +7256,11 @@
       <c r="D61" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E61" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -7261,11 +7273,11 @@
       <c r="D62" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E62" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -7278,11 +7290,11 @@
       <c r="D63" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E63" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -7295,11 +7307,11 @@
       <c r="D64" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -7312,11 +7324,11 @@
       <c r="D65" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E65" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -7329,11 +7341,11 @@
       <c r="D66" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E66" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -7346,11 +7358,11 @@
       <c r="D67" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -7363,11 +7375,11 @@
       <c r="D68" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -7380,11 +7392,11 @@
       <c r="D69" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E69" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -7397,11 +7409,11 @@
       <c r="D70" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E70" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -7414,11 +7426,11 @@
       <c r="D71" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E71" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -7431,11 +7443,11 @@
       <c r="D72" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -7448,11 +7460,11 @@
       <c r="D73" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E73" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -7465,11 +7477,11 @@
       <c r="D74" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E74" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -7482,11 +7494,11 @@
       <c r="D75" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E75" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -7499,11 +7511,11 @@
       <c r="D76" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E76" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -7516,11 +7528,11 @@
       <c r="D77" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E77" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -7533,11 +7545,11 @@
       <c r="D78" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E78" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -7550,11 +7562,11 @@
       <c r="D79" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E79" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E79" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -7567,11 +7579,11 @@
       <c r="D80" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E80" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -7584,11 +7596,11 @@
       <c r="D81" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E81" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -7601,11 +7613,11 @@
       <c r="D82" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E82" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -7618,11 +7630,11 @@
       <c r="D83" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E83" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -7635,11 +7647,11 @@
       <c r="D84" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E84" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -7652,11 +7664,11 @@
       <c r="D85" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E85" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -7669,11 +7681,11 @@
       <c r="D86" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E86" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -7686,11 +7698,11 @@
       <c r="D87" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E87" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -7703,11 +7715,11 @@
       <c r="D88" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E88" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -7720,11 +7732,11 @@
       <c r="D89" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E89" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -7737,11 +7749,11 @@
       <c r="D90" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E90" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -7754,28 +7766,28 @@
       <c r="D91" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E91" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="1" t="s">
         <v>485</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E92" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -7788,11 +7800,11 @@
       <c r="D93" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E93" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -7805,11 +7817,11 @@
       <c r="D94" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E94" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -7822,11 +7834,11 @@
       <c r="D95" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E95" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -7839,11 +7851,11 @@
       <c r="D96" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E96" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -7856,11 +7868,11 @@
       <c r="D97" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E97" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -7873,11 +7885,11 @@
       <c r="D98" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E98" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -7890,11 +7902,11 @@
       <c r="D99" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E99" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -7907,11 +7919,11 @@
       <c r="D100" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E100" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -7924,11 +7936,11 @@
       <c r="D101" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="E101" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E101" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -7941,11 +7953,11 @@
       <c r="D102" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E102" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -7958,11 +7970,11 @@
       <c r="D103" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="E103" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E103" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -7975,11 +7987,11 @@
       <c r="D104" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E104" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -7992,11 +8004,11 @@
       <c r="D105" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E105" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -8009,11 +8021,11 @@
       <c r="D106" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E106" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -8026,11 +8038,11 @@
       <c r="D107" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="E107" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E107" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -8043,11 +8055,11 @@
       <c r="D108" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="E108" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E108" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -8060,11 +8072,11 @@
       <c r="D109" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E109" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -8077,11 +8089,11 @@
       <c r="D110" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E110" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -8094,11 +8106,11 @@
       <c r="D111" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E111" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -8111,11 +8123,11 @@
       <c r="D112" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E112" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -8128,11 +8140,11 @@
       <c r="D113" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E113" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -8145,11 +8157,11 @@
       <c r="D114" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="E114" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -8162,28 +8174,28 @@
       <c r="D115" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="E115" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E115" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>495</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E116" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E116" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -8196,11 +8208,11 @@
       <c r="D117" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="E117" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E117" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -8213,11 +8225,11 @@
       <c r="D118" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="E118" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E118" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -8230,11 +8242,11 @@
       <c r="D119" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="E119" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E119" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -8247,11 +8259,11 @@
       <c r="D120" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="E120" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E120" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -8264,11 +8276,11 @@
       <c r="D121" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="E121" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E121" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -8281,11 +8293,11 @@
       <c r="D122" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="E122" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -8298,28 +8310,28 @@
       <c r="D123" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E123" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="3" t="s">
         <v>499</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="E124" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E124" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -8332,11 +8344,11 @@
       <c r="D125" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="E125" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E125" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -8349,11 +8361,11 @@
       <c r="D126" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E126" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -8366,11 +8378,11 @@
       <c r="D127" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="E127" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -8383,11 +8395,11 @@
       <c r="D128" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="E128" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E128" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -8400,11 +8412,11 @@
       <c r="D129" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="E129" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E129" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -8417,11 +8429,11 @@
       <c r="D130" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E130" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -8434,11 +8446,11 @@
       <c r="D131" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="E131" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E131" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -8451,11 +8463,11 @@
       <c r="D132" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="E132" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E132" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -8468,11 +8480,11 @@
       <c r="D133" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="E133" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E133" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -8485,11 +8497,11 @@
       <c r="D134" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="E134" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E134" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -8502,11 +8514,11 @@
       <c r="D135" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E135" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E135" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -8519,11 +8531,11 @@
       <c r="D136" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="E136" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E136" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -8536,11 +8548,11 @@
       <c r="D137" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="E137" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E137" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -8553,11 +8565,11 @@
       <c r="D138" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="E138" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E138" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -8570,11 +8582,11 @@
       <c r="D139" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="E139" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E139" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -8587,11 +8599,11 @@
       <c r="D140" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E140" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E140" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -8604,11 +8616,11 @@
       <c r="D141" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E141" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E141" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -8621,11 +8633,11 @@
       <c r="D142" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="E142" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E142" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -8638,11 +8650,11 @@
       <c r="D143" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E143" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E143" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -8655,11 +8667,11 @@
       <c r="D144" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="E144" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E144" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -8672,11 +8684,11 @@
       <c r="D145" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="E145" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E145" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -8689,11 +8701,11 @@
       <c r="D146" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="E146" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E146" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -8706,11 +8718,11 @@
       <c r="D147" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="E147" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E147" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -8723,11 +8735,11 @@
       <c r="D148" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="E148" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E148" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -8740,11 +8752,11 @@
       <c r="D149" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="E149" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E149" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -8757,11 +8769,11 @@
       <c r="D150" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E150" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E150" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -8774,11 +8786,11 @@
       <c r="D151" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="E151" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E151" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -8791,11 +8803,11 @@
       <c r="D152" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="E152" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E152" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -8808,11 +8820,11 @@
       <c r="D153" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="E153" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E153" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -8825,11 +8837,11 @@
       <c r="D154" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="E154" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E154" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -8842,11 +8854,11 @@
       <c r="D155" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E155" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E155" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -8859,11 +8871,11 @@
       <c r="D156" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="E156" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E156" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -8876,11 +8888,11 @@
       <c r="D157" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="E157" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E157" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -8893,11 +8905,11 @@
       <c r="D158" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="E158" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E158" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -8910,11 +8922,11 @@
       <c r="D159" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="E159" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E159" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -8927,11 +8939,11 @@
       <c r="D160" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="E160" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E160" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -8944,11 +8956,11 @@
       <c r="D161" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E161" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E161" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -8961,11 +8973,11 @@
       <c r="D162" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="E162" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E162" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -8978,11 +8990,11 @@
       <c r="D163" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="E163" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E163" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -8995,11 +9007,11 @@
       <c r="D164" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="E164" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E164" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -9012,11 +9024,11 @@
       <c r="D165" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="E165" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E165" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -9029,11 +9041,11 @@
       <c r="D166" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="E166" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E166" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -9046,11 +9058,11 @@
       <c r="D167" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="E167" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E167" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -9063,11 +9075,11 @@
       <c r="D168" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="E168" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E168" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -9080,11 +9092,11 @@
       <c r="D169" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="E169" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E169" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -9097,11 +9109,11 @@
       <c r="D170" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="E170" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E170" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -9114,11 +9126,11 @@
       <c r="D171" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="E171" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E171" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -9131,11 +9143,11 @@
       <c r="D172" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="E172" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E172" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -9148,11 +9160,11 @@
       <c r="D173" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="E173" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E173" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -9165,11 +9177,11 @@
       <c r="D174" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E174" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -9182,11 +9194,11 @@
       <c r="D175" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="E175" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E175" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -9199,11 +9211,11 @@
       <c r="D176" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="E176" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E176" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -9216,11 +9228,11 @@
       <c r="D177" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="E177" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E177" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -9233,11 +9245,11 @@
       <c r="D178" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="E178" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E178" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -9250,11 +9262,11 @@
       <c r="D179" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="E179" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E179" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -9267,11 +9279,11 @@
       <c r="D180" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="E180" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E180" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -9284,11 +9296,11 @@
       <c r="D181" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="E181" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E181" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -9301,11 +9313,11 @@
       <c r="D182" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="E182" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E182" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -9318,11 +9330,11 @@
       <c r="D183" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="E183" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E183" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -9335,11 +9347,11 @@
       <c r="D184" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="E184" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E184" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -9352,11 +9364,11 @@
       <c r="D185" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="E185" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E185" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -9369,11 +9381,11 @@
       <c r="D186" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="E186" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E186" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -9386,11 +9398,11 @@
       <c r="D187" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="E187" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E187" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -9403,11 +9415,11 @@
       <c r="D188" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="E188" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E188" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -9420,11 +9432,11 @@
       <c r="D189" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="E189" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E189" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -9437,11 +9449,11 @@
       <c r="D190" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="E190" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E190" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -9454,11 +9466,11 @@
       <c r="D191" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="E191" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E191" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -9471,11 +9483,11 @@
       <c r="D192" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="E192" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E192" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -9488,11 +9500,11 @@
       <c r="D193" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E193" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E193" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -9505,11 +9517,11 @@
       <c r="D194" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="E194" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E194" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -9522,11 +9534,11 @@
       <c r="D195" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="E195" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E195" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -9539,11 +9551,11 @@
       <c r="D196" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="E196" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E196" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -9556,11 +9568,11 @@
       <c r="D197" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E197" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E197" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -9573,11 +9585,11 @@
       <c r="D198" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="E198" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E198" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -9590,11 +9602,11 @@
       <c r="D199" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="E199" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E199" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -9607,11 +9619,11 @@
       <c r="D200" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="E200" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E200" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -9624,11 +9636,11 @@
       <c r="D201" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="E201" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E201" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -9641,11 +9653,11 @@
       <c r="D202" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="E202" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E202" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -9658,11 +9670,11 @@
       <c r="D203" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="E203" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E203" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -9675,11 +9687,11 @@
       <c r="D204" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="E204" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E204" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -9692,11 +9704,11 @@
       <c r="D205" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="E205" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E205" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -9709,11 +9721,11 @@
       <c r="D206" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="E206" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E206" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -9726,11 +9738,11 @@
       <c r="D207" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="E207" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E207" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -9743,11 +9755,11 @@
       <c r="D208" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="E208" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E208" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -9760,11 +9772,11 @@
       <c r="D209" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E209" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E209" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -9777,11 +9789,11 @@
       <c r="D210" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="E210" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E210" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -9794,11 +9806,11 @@
       <c r="D211" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="E211" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E211" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -9811,11 +9823,11 @@
       <c r="D212" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="E212" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E212" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -9828,11 +9840,11 @@
       <c r="D213" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="E213" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E213" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -9845,11 +9857,11 @@
       <c r="D214" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="E214" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E214" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -9862,11 +9874,11 @@
       <c r="D215" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="E215" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E215" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -9879,11 +9891,11 @@
       <c r="D216" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="E216" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E216" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -9896,11 +9908,11 @@
       <c r="D217" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="E217" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E217" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -9913,11 +9925,11 @@
       <c r="D218" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="E218" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E218" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -9930,11 +9942,11 @@
       <c r="D219" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="E219" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E219" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -9947,11 +9959,11 @@
       <c r="D220" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="E220" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E220" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -9964,11 +9976,11 @@
       <c r="D221" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="E221" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E221" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -9981,11 +9993,11 @@
       <c r="D222" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="E222" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E222" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -9998,11 +10010,11 @@
       <c r="D223" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="E223" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E223" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -10015,11 +10027,11 @@
       <c r="D224" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="E224" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E224" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -10032,11 +10044,11 @@
       <c r="D225" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="E225" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E225" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -10049,11 +10061,11 @@
       <c r="D226" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E226" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E226" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -10066,11 +10078,11 @@
       <c r="D227" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E227" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E227" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -10083,11 +10095,11 @@
       <c r="D228" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="E228" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E228" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -10100,11 +10112,11 @@
       <c r="D229" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="E229" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E229" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -10117,11 +10129,11 @@
       <c r="D230" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="E230" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E230" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -10134,11 +10146,11 @@
       <c r="D231" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="E231" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E231" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -10151,11 +10163,11 @@
       <c r="D232" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="E232" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E232" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -10168,11 +10180,11 @@
       <c r="D233" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="E233" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E233" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -10185,11 +10197,11 @@
       <c r="D234" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="E234" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E234" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -10202,11 +10214,11 @@
       <c r="D235" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="E235" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E235" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -10219,11 +10231,11 @@
       <c r="D236" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="E236" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E236" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -10236,11 +10248,11 @@
       <c r="D237" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="E237" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E237" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -10253,11 +10265,11 @@
       <c r="D238" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="E238" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E238" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -10270,11 +10282,11 @@
       <c r="D239" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="E239" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E239" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -10287,11 +10299,11 @@
       <c r="D240" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="E240" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E240" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -10304,11 +10316,11 @@
       <c r="D241" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="E241" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E241" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -10321,11 +10333,11 @@
       <c r="D242" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="E242" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E242" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -10338,11 +10350,11 @@
       <c r="D243" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="E243" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E243" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -10355,28 +10367,28 @@
       <c r="D244" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="E244" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E244" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>244</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C245" s="3" t="s">
+      <c r="C245" s="1" t="s">
         <v>493</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="E245" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E245" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -10389,11 +10401,11 @@
       <c r="D246" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E246" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E246" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -10406,11 +10418,11 @@
       <c r="D247" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="E247" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E247" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -10423,11 +10435,11 @@
       <c r="D248" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="E248" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E248" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -10440,11 +10452,11 @@
       <c r="D249" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="E249" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E249" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -10457,11 +10469,11 @@
       <c r="D250" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="E250" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E250" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -10474,58 +10486,58 @@
       <c r="D251" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="E251" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E251" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>251</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C252" s="3" t="s">
+      <c r="C252" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="D252" s="3" t="s">
+      <c r="D252" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="E252" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E252" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>252</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B253" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C253" s="3" t="s">
+      <c r="C253" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="D253" s="3" t="s">
+      <c r="D253" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="E253" s="5" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E253" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>252</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="C254" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="D254" s="3" t="s">
+      <c r="D254" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="E254" s="5" t="s">
+      <c r="E254" s="4" t="s">
         <v>750</v>
       </c>
     </row>

--- a/data/BRM.xlsx
+++ b/data/BRM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F701D4DC-A99F-4765-8310-C5CBFA7CA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA5D0B7-E0D3-4B55-A584-91908FC922EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7F7ADE42-7E02-4ACE-BDAF-072FCF0085B8}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="765">
   <si>
     <t>Roll No</t>
   </si>
@@ -2337,6 +2337,9 @@
   </si>
   <si>
     <t>Sritam Tripathy</t>
+  </si>
+  <si>
+    <t>25P055</t>
   </si>
 </sst>
 </file>
@@ -5375,7 +5378,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>418</v>
+        <v>764</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>763</v>
